--- a/myG All Store.xlsx
+++ b/myG All Store.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
   <si>
     <t>Store</t>
   </si>
@@ -462,6 +462,9 @@
   </si>
   <si>
     <t>THRIPUNITHURA FUTURE</t>
+  </si>
+  <si>
+    <t>CHERTHALA FUTURE</t>
   </si>
 </sst>
 </file>
@@ -1143,7 +1146,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1679,7 +1682,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A145"/>
+  <dimension ref="A1:A146"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="28.6666666666667" customWidth="1"/>
@@ -2406,8 +2409,13 @@
       </c>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="8" t="s">
+      <c r="A145" s="5" t="s">
         <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="8" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/myG All Store.xlsx
+++ b/myG All Store.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <si>
     <t>Store</t>
   </si>
@@ -462,9 +462,6 @@
   </si>
   <si>
     <t>THRIPUNITHURA FUTURE</t>
-  </si>
-  <si>
-    <t>CHERTHALA FUTURE</t>
   </si>
 </sst>
 </file>
@@ -1146,7 +1143,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1682,7 +1679,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A146"/>
+  <dimension ref="A1:A145"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="28.6666666666667" customWidth="1"/>
@@ -2409,13 +2406,8 @@
       </c>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="5" t="s">
+      <c r="A145" s="8" t="s">
         <v>144</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="8" t="s">
-        <v>145</v>
       </c>
     </row>
   </sheetData>
